--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
@@ -504,7 +504,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>40</v>
@@ -532,7 +532,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -574,7 +574,7 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -588,7 +588,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -680,6 +680,9 @@
       <c r="A18" t="n">
         <v>18</v>
       </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -758,6 +761,9 @@
       <c r="A30" t="n">
         <v>30</v>
       </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
       <c r="D30" t="n">
         <v>15</v>
       </c>
@@ -766,6 +772,9 @@
       <c r="A31" t="n">
         <v>31</v>
       </c>
+      <c r="C31" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -877,6 +886,14 @@
       </c>
       <c r="C45" t="n">
         <v>97</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -484,16 +484,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -501,13 +501,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -515,13 +518,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
@@ -538,7 +544,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -546,13 +552,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -560,10 +569,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -579,6 +591,9 @@
       <c r="D8" t="n">
         <v>8</v>
       </c>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -593,22 +608,25 @@
       <c r="D9" t="n">
         <v>3</v>
       </c>
+      <c r="E9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
         <v>20</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -616,16 +634,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -633,16 +651,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
       <c r="D13" t="n">
         <v>30</v>
       </c>
@@ -652,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -767,6 +794,9 @@
       <c r="D30" t="n">
         <v>15</v>
       </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -830,6 +860,12 @@
       </c>
       <c r="B38" t="n">
         <v>30</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -487,7 +487,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>30</v>
@@ -654,7 +654,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>32</v>
@@ -670,6 +670,9 @@
       <c r="B13" t="n">
         <v>20</v>
       </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
       <c r="D13" t="n">
         <v>30</v>
       </c>
@@ -733,6 +736,9 @@
     <row r="21">
       <c r="A21" t="n">
         <v>21</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>18</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,22 +478,38 @@
           <t>Finalterm</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Quiz</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +520,19 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -527,6 +549,12 @@
         <v>40</v>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -535,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
@@ -620,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -503,7 +503,7 @@
         <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -526,7 +526,7 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -494,7 +494,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -506,10 +506,10 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -517,10 +517,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
@@ -529,7 +529,7 @@
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -540,10 +540,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>40</v>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -591,6 +591,9 @@
       <c r="E6" t="n">
         <v>33</v>
       </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -796,6 +799,9 @@
     <row r="25">
       <c r="A25" t="n">
         <v>25</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="26">

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -509,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -532,7 +532,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>40</v>
@@ -555,7 +555,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -563,10 +563,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -503,10 +503,10 @@
         <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -494,7 +494,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -506,10 +506,10 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -517,10 +517,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
@@ -529,7 +529,7 @@
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
@@ -540,10 +540,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>40</v>
@@ -563,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
@@ -580,10 +580,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -592,7 +592,7 @@
         <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -625,6 +625,9 @@
       <c r="E8" t="n">
         <v>18</v>
       </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -889,6 +892,9 @@
       </c>
       <c r="B37" t="n">
         <v>88</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>20</v>

--- a/intelligent_voice_assistant/database/student_marks.xlsx
+++ b/intelligent_voice_assistant/database/student_marks.xlsx
@@ -494,7 +494,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -506,7 +506,7 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -529,7 +529,7 @@
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
